--- a/sst-audit/data/audit_report.xlsx
+++ b/sst-audit/data/audit_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,7 +509,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>B21</t>
+          <t>B23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,19 +561,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.16-2-3
-Поправка: Гл.6.Прил.2.2.п.2.2.6_06.00.01.07.001
+          <t>4.10-174-2
 Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Прокладка по стенам зданий и в каналах труб чугунных напорных раструбных диаметром 100 мм</t>
+          <t>Монтаж наружной камеры видеонаблюдения</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B23</t>
+          <t>B25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -623,19 +622,15 @@
       <c r="B4" t="n">
         <v>0</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1.12-1-69</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Узлы трубопроводов из чугунных канализационных труб с фасонными частями, диаметр условного прохода 100 мм</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>B29</t>
+          <t>B31</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -659,13 +654,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>50.5</v>
+        <v>90</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>50.5</v>
+        <v>90</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -688,12 +683,12 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>НР от ФОТ</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B30</t>
+          <t>B32</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -717,13 +712,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -746,12 +741,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>СП от ФОТ</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B31</t>
+          <t>B33</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -775,13 +770,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>61</v>
+        <v>25.33</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>61</v>
+        <v>25.33</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -795,58 +790,64 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>SUSPECT</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>83.2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Прайс-лист</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ЗТР</t>
+          <t>ОБОРУДОВАНИЕ:
+Цилиндрическая IP-видеокамера с фиксированным объективом IP 4 Мп; размер матрицы 1/2.9"; встроенный микрофон; Дальность ИК подсветки 80м; режим "день/ночь"; PoE 7 Вт; -40 ~ +60°C, (2/8-12)
+1 236,60 = [10 913 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B32</t>
+          <t>B37</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>IP-видеокамера купольная 4Мп с фиксированным объективом 2,8мм</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.1 [row 4]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L7" t="n">
-        <v>116</v>
+        <v>-12</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+          <t>[HITL Подтверждено] Занижение объема относительно РД</t>
         </is>
       </c>
     </row>
@@ -861,17 +862,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.12-10-16</t>
+          <t>4.10-136-1
+Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ревизия чугунная, диаметр условного прохода 100 мм</t>
+          <t>Монтаж коробки телевизионной (ответвители, разветвители магистральные, домовые, абонентские), УСС, БФТК</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>B40</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -895,13 +897,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -921,21 +923,15 @@
       <c r="B9" t="n">
         <v>0</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.16-28-2
-Поправка: Гл.6.Прил.2.2.п.2.2.6_06.00.01.07.001
-Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Врезки в действующие внутренние сети трубопроводов канализации диаметром 100 мм</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>B39</t>
+          <t>B43</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -959,13 +955,13 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -988,7 +984,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>НР от ФОТ</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1046,7 +1042,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>СП от ФОТ</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1075,13 +1071,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>61</v>
+        <v>0.8</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>61</v>
+        <v>0.8</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1095,58 +1091,64 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Прайс-лист</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ЗТР</t>
+          <t>ОБОРУДОВАНИЕ:
+Устройство грозозащиты 
+326,34 = [2 880 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B46</t>
+          <t>B49</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Устройство грозозащиты</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.1 [row 3]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8.94</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>8.94</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+          <t>Объемы соответствуют проектным с учетом допустимого расхода и погрешностей</t>
         </is>
       </c>
     </row>
@@ -1161,19 +1163,18 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.16-13-2
-Поправка: Гл.6.Прил.2.2.п.2.2.6_06.00.01.07.001
+          <t>4.10-174-1
 Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов канализации из ПВХ труб диаметром 100 мм - 150 мм</t>
+          <t>Монтаж внутренней камеры видеонаблюдения</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B50</t>
+          <t>B52</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1197,13 +1198,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.62</v>
+        <v>1.7</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.62</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1223,19 +1224,15 @@
       <c r="B14" t="n">
         <v>0</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1.12-2-1167</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Хомуты из оцинкованной стали с резиновыми прокладками для жесткого и скользящего крепления полипропиленовых труб, наружный диаметр 110 мм</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B56</t>
+          <t>B58</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1259,13 +1256,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1285,19 +1282,15 @@
       <c r="B15" t="n">
         <v>0</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1.12-1-80</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Заготовка трубная из непластифицированного поливинилхлорида, для внутренней канализации, без средств крепления, диаметр 110 мм</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B57</t>
+          <t>B59</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1321,13 +1314,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1347,19 +1340,15 @@
       <c r="B16" t="n">
         <v>0</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1.12-5-133</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ревизия из полиэтилена, диаметр 110 мм</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>B58</t>
+          <t>B60</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1383,13 +1372,13 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>15.54</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>15.54</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1403,58 +1392,64 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Прайс-лист</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>НР от ФОТ</t>
+          <t>ОБОРУДОВАНИЕ:
+IP-видеокамера купольная 4Мп с фиксированным объективом 2,8мм  
+1 585,28 = [13 990 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>B59</t>
+          <t>B64</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>IP-видеокамера купольная 4Мп с фиксированным объективом 2,8мм</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.1 [row 4]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+          <t>Объемы соответствуют проектным с учетом допустимого расхода и погрешностей</t>
         </is>
       </c>
     </row>
@@ -1467,15 +1462,20 @@
       <c r="B18" t="n">
         <v>0</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4.10-72-14
+Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>СП от ФОТ</t>
+          <t>Монтаж устройства цифровой регистрации</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>B60</t>
+          <t>B67</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1528,12 +1528,12 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ЗТР</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>B61</t>
+          <t>B70</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1583,19 +1583,15 @@
       <c r="B20" t="n">
         <v>0</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1.12-5-134</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Крышка ревизии из полиэтилена, диаметр 110 мм</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>B65</t>
+          <t>B71</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1619,13 +1615,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1645,19 +1641,15 @@
       <c r="B21" t="n">
         <v>0</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1.12-5-133</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ревизия из полиэтилена, диаметр 110 мм / прочистка</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>B72</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1681,13 +1673,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1701,62 +1693,64 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.1-1-59</t>
+          <t>Прайс-лист</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Болты строительные анкерные с гайками</t>
+          <t>ОБОРУДОВАНИЕ:
+Видеорегистратор до 32 IP-видеокамер 
+2 275,93 = [20 085 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>B71</t>
+          <t>B76</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Видеорегистратор до 32 IP-видеокамер</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.1 [row 5]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>т</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+          <t>Объемы соответствуют проектным с учетом допустимого расхода и погрешностей</t>
         </is>
       </c>
     </row>
@@ -1771,19 +1765,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.16-13-1
-Поправка: Гл.6.Прил.2.2.п.2.2.6_06.00.01.07.001
+          <t>4.10-34-5
 Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Прокладка трубопроводов канализации из ПВХ труб диаметром до 50 мм</t>
+          <t>Монтаж коммутатора служебной связи</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>B75</t>
+          <t>B79</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1807,13 +1800,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1833,19 +1826,15 @@
       <c r="B24" t="n">
         <v>0</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1.12-2-1165</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Хомуты из оцинкованной стали с резиновыми прокладками для жесткого и скользящего крепления полипропиленовых труб, наружный диаметр 50 мм</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>B81</t>
+          <t>B84</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1869,13 +1858,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1895,19 +1884,15 @@
       <c r="B25" t="n">
         <v>0</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1.12-1-79</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Заготовка трубная из непластифицированного поливинилхлорида, для внутренней канализации, без средств крепления, диаметр 50 мм</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>B82</t>
+          <t>B85</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1931,13 +1916,13 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -1957,19 +1942,15 @@
       <c r="B26" t="n">
         <v>0</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1.12-5-97</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ревизия из полиэтилена низкого давления, с крышкой, для канализации, диаметр 50 мм / прочистка</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>B83</t>
+          <t>B86</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1993,13 +1974,13 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>6.2</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>6.2</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2013,58 +1994,64 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Прайс-лист</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>НР от ФОТ</t>
+          <t>ОБОРУДОВАНИЕ:
+Коммутатор сетевой 
+4 798,88 = [42 350 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>B84</t>
+          <t>B90</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Коммутатор сетевой</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.1 [row 6]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+          <t>Объемы соответствуют проектным с учетом допустимого расхода и погрешностей</t>
         </is>
       </c>
     </row>
@@ -2077,15 +2064,20 @@
       <c r="B28" t="n">
         <v>0</v>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4.10-32-4
+Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>СП от ФОТ</t>
+          <t>Монтаж платы дополнительной, устанавливаемой на готовом месте стойки</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>B85</t>
+          <t>B93</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2109,13 +2101,13 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2138,12 +2130,12 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ЗТР</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>B86</t>
+          <t>B98</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2167,13 +2159,13 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>58.4</v>
+        <v>90</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>58.4</v>
+        <v>90</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2193,19 +2185,15 @@
       <c r="B30" t="n">
         <v>0</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1.1-1-59</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Болты строительные анкерные с гайками</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>B90</t>
+          <t>B99</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2225,17 +2213,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>т</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>13.8</v>
+        <v>46</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>13.8</v>
+        <v>46</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2255,21 +2243,15 @@
       <c r="B31" t="n">
         <v>0</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>3.16-33-1
-Поправка: Гл.6.Прил.2.2.п.2.2.6_06.00.01.07.001
-Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Установка противопожарных муфт на канализационных стояках из полипропиленовых труб в междуэтажных перекрытиях, муфт обжимных</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>B94</t>
+          <t>B100</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2289,17 +2271,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>15</v>
+        <v>2.1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>15</v>
+        <v>2.1</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2319,15 +2301,21 @@
       <c r="B32" t="n">
         <v>0</v>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Прайс-лист</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>НР от ФОТ</t>
+          <t>ОБОРУДОВАНИЕ:
+Модуль защиты 
+220,86 = [1 949 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>B97</t>
+          <t>B104</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2347,17 +2335,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2377,15 +2365,21 @@
       <c r="B33" t="n">
         <v>0</v>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Прайс-лист</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>СП от ФОТ</t>
+          <t>ОБОРУДОВАНИЕ:
+Универсальный корпус 19"
+363,07 = [3 204 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B98</t>
+          <t>B107</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2405,17 +2399,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2435,15 +2429,20 @@
       <c r="B34" t="n">
         <v>0</v>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>4.11-7-1
+Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ЗТР</t>
+          <t>Установка аппарата настольного массой до 0,015 т</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B99</t>
+          <t>B110</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2467,13 +2466,13 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>14.63</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>14.63</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -2493,19 +2492,15 @@
       <c r="B35" t="n">
         <v>0</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1.12-5-542</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Муфта противопожарная из нержавеющей стали, с вкладышем из терморасширяющейся резины, для трубы диаметром 50 мм</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>B103</t>
+          <t>B114</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2529,13 +2524,13 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -2555,19 +2550,15 @@
       <c r="B36" t="n">
         <v>0</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1.12-5-456</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Муфта противопожарная из нержавеющей стали, с вкладышем из терморасширяющейся резины, для трубы диаметром 110 мм</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>B106</t>
+          <t>B115</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2591,13 +2582,13 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -2617,21 +2608,15 @@
       <c r="B37" t="n">
         <v>0</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>3.22-27-3
-Поправка: Гл.6.Прил.2.2.п.2.2.6_06.00.01.07.001
-Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Промывка без дезинфекции трубопроводов диаметром 100 мм / промывка сущ.выпусков канализации диам100мм гидродинамическим способом</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>B109</t>
+          <t>B116</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2655,13 +2640,13 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.01</v>
+        <v>1.03</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.01</v>
+        <v>1.03</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -2681,15 +2666,21 @@
       <c r="B38" t="n">
         <v>0</v>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Прайс-лист</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>НР от ФОТ</t>
+          <t>ОБОРУДОВАНИЕ:
+Автоматизированное рабочее место, моноблок 
+16 661,80 = [147 040 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>B113</t>
+          <t>B120</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2709,17 +2700,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2739,15 +2730,20 @@
       <c r="B39" t="n">
         <v>0</v>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>13.1-14-104</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>СП от ФОТ</t>
+          <t>ОБОРУДОВАНИЕ:_x000D_
+Клавиатура компьютерная проводная, интерфейс USB. Материал корпуса пластик, влагозащищенная конструкция, индикатор Caps Lock, индикатор Num Lock</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>B114</t>
+          <t>B123</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2771,13 +2767,13 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2797,15 +2793,20 @@
       <c r="B40" t="n">
         <v>0</v>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>13.1-14-105</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ЗТР</t>
+          <t>ОБОРУДОВАНИЕ:_x000D_
+Мышь компьютерная проводная оптическая, интерфейс USB</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>B115</t>
+          <t>B126</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2829,13 +2830,13 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>20.6</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>20.6</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2857,19 +2858,18 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3.26-16-1
-Поправка: Гл.6.Прил.2.2.п.2.2.6_06.00.01.07.001
+          <t>4.10-27-4
 Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Изоляция трубопроводов изделиями из вспененного каучука, вспененного полиэтилена, трубками</t>
+          <t>Прокладка и включение перемычки кабельной между секциями одного статива без укладки в кабельном канале</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>B119</t>
+          <t>B129</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2893,13 +2893,13 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>1.5</v>
+        <v>0.27</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>0.27</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2919,19 +2919,15 @@
       <c r="B42" t="n">
         <v>0</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1.1-1-2543</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Лента армированная с клеевым слоем, универсального применения, типа ТПЛ, ширина 50 мм, серая</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>B125</t>
+          <t>B132</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2955,13 +2951,13 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>22.5</v>
+        <v>90</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>22.5</v>
+        <v>90</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2981,19 +2977,15 @@
       <c r="B43" t="n">
         <v>0</v>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1.1-1-2544</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Клей контактный, на основе полихлоропренового каучука, температура эксплуатации от -40 до +105°С, для приклеивания листовых и трубчатых каучуковых теплоизоляционных материалов</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>B126</t>
+          <t>B133</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3017,13 +3009,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>0.36</v>
+        <v>46</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.36</v>
+        <v>46</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3046,12 +3038,12 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>НР от ФОТ</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>B127</t>
+          <t>B134</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3075,13 +3067,13 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>87</v>
+        <v>3.1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>87</v>
+        <v>3.1</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -3095,178 +3087,189 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" t="inlineStr"/>
+        <v>87.5</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Прайс-лист</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>СП от ФОТ</t>
+          <t>Коммутационный шнур (патч-корд) кат.5E 1м синий 
+19,68 = [239,53 / 1,22 /  10,18] +  2% Заг.скл</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>B128</t>
+          <t>B138</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Коммутационный шнур (патч-корд) кат.5E UTP LSZH 1м синий</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.1 [row 13]</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L45" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>0.271</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+          <t>Объемы соответствуют проектным с учетом допустимого расхода и погрешностей</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" t="inlineStr"/>
+        <v>88.2</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Прайс-лист</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ЗТР</t>
+          <t>Изолирующий колпачек для разъемов 
+0,32 = [3,79 / 1,22 /  10,18] +  2% Заг.скл</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>B129</t>
+          <t>B141</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Изолирующий колпачек для разъемов RG45</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.1 [row 17]</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>2.2</v>
+        <v>30</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+          <t>Объемы соответствуют проектным с учетом допустимого расхода и погрешностей</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>88.5</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.1-1-3853</t>
+          <t>Прайс-лист</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена с закрытой ячеистой структурой, для тепло- и шумоизоляции внутренних инженерных систем, температура применения до +95°C, коэффициент теплопроводности при температуре +10°C не более 0,038 Вт/(м х К), группа горючести Г1, внутренний диаметр 133 мм, толщина 13 мм</t>
+          <t>Mонтажная коробка для цилиндрических камер на стену, white
+231,11 = [2 814 / 1,22 /  10,18] +  2% Заг.скл</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>B133</t>
+          <t>B144</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mонтажная коробка для цилиндрических камер на стену</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.2 [row 18]</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>15.75</v>
+        <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L47" t="n">
-        <v>15.75</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+          <t>Объемы соответствуют проектным с учетом допустимого расхода и погрешностей</t>
         </is>
       </c>
     </row>
@@ -3281,19 +3284,18 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3.17-14-3
-Поправка: Гл.6.Прил.2.2.п.2.2.6_06.00.01.07.001
+          <t>4.10-173-2
 Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Установка подвесного унитаза</t>
+          <t>Монтаж блока бесперебойного питания (ББП) в диспетчерской</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>B141</t>
+          <t>B147</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3317,13 +3319,13 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -3343,19 +3345,15 @@
       <c r="B49" t="n">
         <v>0</v>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1.17-1-85</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Унитаз керамический, подвесной для систем инсталляции, безободковый, с сидением микролифт, с горизонтальным выпуском</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>B146</t>
+          <t>B150</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3379,13 +3377,13 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -3408,12 +3406,12 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>НР от ФОТ</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>B147</t>
+          <t>B151</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3437,13 +3435,13 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -3466,12 +3464,12 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>СП от ФОТ</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>B148</t>
+          <t>B152</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3495,13 +3493,13 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>61</v>
+        <v>3.18</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>61</v>
+        <v>3.18</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -3521,15 +3519,21 @@
       <c r="B52" t="n">
         <v>0</v>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Прайс-лист</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ЗТР</t>
+          <t>ОБОРУДОВАНИЕ:
+Источник бесперебойного питания 1500 Вт,36В (3x9Ач)
+7 525,80 = [66 415 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>B149</t>
+          <t>B156</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3549,17 +3553,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -3581,17 +3585,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.17-2-45</t>
+          <t>4.11-12-1
+Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Отвод из поливинилхлорида гофрированный для унитаза, диаметр 110 мм</t>
+          <t>Установка съемных и выдвижных блоков (модулей, ячеек, ТЭЗ) массой до 5 кг</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>B153</t>
+          <t>B163</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3615,13 +3620,13 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -3641,19 +3646,15 @@
       <c r="B54" t="n">
         <v>0</v>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1.12-8-50</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Манжета резиновая, ступенчатая или конусная, для унитазов</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>B156</t>
+          <t>B167</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3677,13 +3678,13 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -3703,21 +3704,15 @@
       <c r="B55" t="n">
         <v>0</v>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>3.17-14-1
-Поправка: Гл.6.Прил.2.2.п.2.2.6_06.00.01.07.001
-Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Установка комплекта инсталляции</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>B159</t>
+          <t>B168</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3741,13 +3736,13 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -3767,19 +3762,15 @@
       <c r="B56" t="n">
         <v>0</v>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1.17-1-83</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Система инсталляции рамного типа, для подвесных унитазов, с клавишей, два режима смыва, объем смывного бака 9 литров, ширина 500 мм, глубина 160 мм, высота 1130 мм, с крепежными элементами</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>B164</t>
+          <t>B169</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3803,13 +3794,13 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -3823,58 +3814,65 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" t="inlineStr"/>
+        <v>80.8</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Прайс-лист</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>НР от ФОТ</t>
+          <t>ОБОРУДОВАНИЕ:
+1U патч-панель кат.5E 24 порта высокой  плотности 
+493,37 = [4 354 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>B165</t>
+          <t>B173</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1U патч-панель кат.5E UTP 24 порта (Dual IDC) высокой
+плотности Кабельные изделия</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.1 [row 11]</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+          <t>[HITL Подтверждено] Объемы соответствуют проектным с учетом допустимого расхода и погрешностей</t>
         </is>
       </c>
     </row>
@@ -3887,15 +3885,20 @@
       <c r="B58" t="n">
         <v>0</v>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>4.10-186-5
+Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>СП от ФОТ</t>
+          <t>Прокладка кабеля связи симметричного для цифровых систем передачи в трубах гофрированных: по бетонным и кирпичным поверхностям стен и потолка</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>B166</t>
+          <t>B180</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3915,17 +3918,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>м</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>61</v>
+        <v>1000</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>61</v>
+        <v>1000</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -3945,15 +3948,19 @@
       <c r="B59" t="n">
         <v>0</v>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1.12-5-372</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ЗТР</t>
+          <t>Трубы электротехнические, гофрированные, из ПВХ, негорючие, с зондом, наружный диаметр 20 мм</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>B167</t>
+          <t>B185</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3973,17 +3980,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>м</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1.15</v>
+        <v>1020</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>1.15</v>
+        <v>1020</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -4005,19 +4012,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3.17-3-7
-Поправка: Гл.6.Прил.2.2.п.2.2.6_06.00.01.07.001
-Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
+          <t>1.21-5-1136</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Установка унитазов с бачком непосредственно присоединенным</t>
+          <t>Держатель пластиковый с защелкой для крепления труб, рукавов и гибких вводов диаметром 20 мм</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>B171</t>
+          <t>B186</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4041,13 +4046,13 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>0.1</v>
+        <v>21.64</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0.1</v>
+        <v>21.64</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -4067,19 +4072,15 @@
       <c r="B61" t="n">
         <v>0</v>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1.17-1-79</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Унитаз-компакт керамический нестандартной высоты для маломобильных групп населения с горизонтальным выпуском</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>B177</t>
+          <t>B187</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4103,13 +4104,13 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -4132,12 +4133,12 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>НР от ФОТ</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>B178</t>
+          <t>B188</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4161,13 +4162,13 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -4190,12 +4191,12 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>СП от ФОТ</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>B179</t>
+          <t>B189</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4219,13 +4220,13 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>61</v>
+        <v>16.6</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>61</v>
+        <v>16.6</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -4245,15 +4246,20 @@
       <c r="B64" t="n">
         <v>0</v>
       </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>4.8-280-2
+Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ЗТР</t>
+          <t>Прокладка пластикового кабель-канала по бетонному основанию</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>B180</t>
+          <t>B193</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4273,17 +4279,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>м</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>7.77</v>
+        <v>300</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>7.77</v>
+        <v>300</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -4305,17 +4311,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1.17-3-1</t>
+          <t>1.1-1-1962</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Сиденье пластиковое с крышкой к унитазам</t>
+          <t>Кабель-канал, размер 10х15 мм/10х12мм</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>B184</t>
+          <t>B199</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4335,17 +4341,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>м</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -4365,19 +4371,15 @@
       <c r="B66" t="n">
         <v>0</v>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1.17-2-45</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Отвод из поливинилхлорида гофрированный для унитаза, диаметр 110 мм</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>B187</t>
+          <t>B200</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4401,13 +4403,13 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -4427,19 +4429,15 @@
       <c r="B67" t="n">
         <v>0</v>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1.12-8-50</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Манжета резиновая, ступенчатая или конусная, для унитазов</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>B190</t>
+          <t>B201</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4463,13 +4461,13 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -4489,21 +4487,15 @@
       <c r="B68" t="n">
         <v>0</v>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>3.17-1-20
-Поправка: Гл.6.Прил.2.2.п.2.2.6_06.00.01.07.001
-Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Установка раковин (умывальников) керамических</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>B193</t>
+          <t>B202</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4527,13 +4519,13 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>0.1</v>
+        <v>40.67</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0.1</v>
+        <v>40.67</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -4555,17 +4547,18 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1.17-2-8</t>
+          <t>4.8-174-1
+Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Сифон бутылочный латунный</t>
+          <t>Прокладка металлического рукава, наружный диаметр до 48 мм</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>B199</t>
+          <t>B206</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4585,17 +4578,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>м</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -4615,15 +4608,19 @@
       <c r="B70" t="n">
         <v>0</v>
       </c>
-      <c r="C70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1.21-5-435</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>НР от ФОТ</t>
+          <t>Рукав металлический, типа РЗ-ЦХ, из стальной оцинкованной ленты, негерметичный, с уплотнением хлопчатобумажной нитью, условный диаметр 20 мм</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>B200</t>
+          <t>B212</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4643,17 +4640,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>м</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>109</v>
+        <v>10.3</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>109</v>
+        <v>10.3</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -4676,12 +4673,12 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>СП от ФОТ</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>B201</t>
+          <t>B213</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4705,13 +4702,13 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -4734,12 +4731,12 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ЗТР</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>B202</t>
+          <t>B214</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4763,13 +4760,13 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>6.33</v>
+        <v>51</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>6.33</v>
+        <v>51</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -4789,20 +4786,15 @@
       <c r="B73" t="n">
         <v>0</v>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Прайс-лист</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Умывальник для маломобильных граждан. Форма прямоугольная с выемкой на фронтальной поверхности
-1 109,56 = [13 510 / 1,22 /  10,18] +  2% Заг.скл</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>B206</t>
+          <t>B215</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4822,17 +4814,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>29.9</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>29.9</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -4854,17 +4846,18 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1.17-2-25</t>
+          <t>4.8-162-1
+Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Выпуск пластмассовый к санитарно-техническим приборам</t>
+          <t>Прокладка в коробах провода сечением до 6 мм2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>B209</t>
+          <t>B219</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4884,17 +4877,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>м</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -4914,19 +4907,15 @@
       <c r="B75" t="n">
         <v>0</v>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1.17-2-31</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Кронштейн стальной для умывальников и моек, скрытый, большой, длина 320 мм</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>B212</t>
+          <t>B225</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4950,13 +4939,13 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -4976,21 +4965,15 @@
       <c r="B76" t="n">
         <v>0</v>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>3.17-1-20
-Поправка: Гл.6.Прил.2.2.п.2.2.6_06.00.01.07.001
-Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Установка раковин (умывальников) керамических</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>B215</t>
+          <t>B226</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5014,13 +4997,13 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>0.5</v>
+        <v>51</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0.5</v>
+        <v>51</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -5040,19 +5023,15 @@
       <c r="B77" t="n">
         <v>0</v>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1.17-2-8</t>
-        </is>
-      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Сифон бутылочный латунный</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>B221</t>
+          <t>B227</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5076,13 +5055,13 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>5</v>
+        <v>3.09</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>5</v>
+        <v>3.09</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -5096,58 +5075,65 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>SUSPECT</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Прайс-лист</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>НР от ФОТ</t>
+          <t>Кабель витая пара U/UTP в общем экране, cat 5e, 4х2х0.52,  оболочка из ПВХ пластиката пониженной пожарной опасности с  низким дымо- и газовыделением, цвет оболочки зеленый  U/UTP Cat5e типа  PVCLS нг(A)-HFx4x2x0.52
+7,81 = [95,09 / 1,22 /  10,18] +  2% Заг.скл</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>B222</t>
+          <t>B231</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Кабель витая пара U/UTP в общем экране, cat 5e, 4х2х0.52,
+оболочка из ПВХ пластиката пониженной пожарной опасности с
+низким дымо- и газовыделением, цвет оболочки зеленый</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.1 [row 12]</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>м</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>109</v>
+        <v>1326</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="L78" t="n">
-        <v>109</v>
+        <v>-52</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>13.781</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+          <t>Занижение объема относительно РД</t>
         </is>
       </c>
     </row>
@@ -5160,15 +5146,20 @@
       <c r="B79" t="n">
         <v>0</v>
       </c>
-      <c r="C79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>4.10-32-1
+Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>СП от ФОТ</t>
+          <t>Монтаж стойки, полустойки, каркаса стойки или шкафа массой до 100 кг</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>B223</t>
+          <t>B238</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5192,13 +5183,13 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -5221,12 +5212,12 @@
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ЗТР</t>
+          <t>НР от ФОТ</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>B224</t>
+          <t>B243</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5250,13 +5241,13 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>6.33</v>
+        <v>90</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>6.33</v>
+        <v>90</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -5276,19 +5267,15 @@
       <c r="B81" t="n">
         <v>0</v>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1.17-2-25</t>
-        </is>
-      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Выпуск пластмассовый к санитарно-техническим приборам</t>
+          <t>СП от ФОТ</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>B228</t>
+          <t>B244</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5312,13 +5299,13 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -5338,19 +5325,15 @@
       <c r="B82" t="n">
         <v>0</v>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1.17-2-31</t>
-        </is>
-      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Кронштейн стальной для умывальников и моек, скрытый, большой, длина 320 мм</t>
+          <t>ЗТР</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>B231</t>
+          <t>B245</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5374,13 +5357,13 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -5394,11 +5377,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -5407,28 +5390,32 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Умывальник фаянсовый с отверстием для предотвращения перелива
-432,82 = [5 270 / 1,22 /  10,18] +  2% Заг.скл</t>
+          <t>ОБОРУДОВАНИЕ:
+Шкаф монтажный телекоммуникационный 19" напольный  для распределительного и серверного оборудования 32U  600x600x1610mm (ШхГхВ) передняя стеклянная и задняя сплошная  металлическая двери, ручка с замком, цвет серый
+5 921,61 = [52 258 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>B235</t>
+          <t>B249</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Шкаф Cabeus монтажный телекоммуникационный 19" напольный
+для распределительного и серверного оборудования 32U
+600x600x1610mm (ШхГхВ) передняя стеклянная и задняя сплошная
+металлическая двери, ручка с замком, цвет серый (RAL 7035)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.2 [row 21]</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5437,20 +5424,20 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+          <t>Объемы соответствуют проектным с учетом допустимого расхода и погрешностей</t>
         </is>
       </c>
     </row>
@@ -5465,19 +5452,18 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>3.16-21-2
-Поправка: Гл.6.Прил.2.2.п.2.2.6_06.00.01.07.001
+          <t>4.11-12-1
 Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Установка воронок сливных диаметром 50 мм</t>
+          <t>Установка съемных и выдвижных блоков (модулей, ячеек, ТЭЗ) массой до 5 кг</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>B238</t>
+          <t>B252</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5501,13 +5487,13 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -5535,7 +5521,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>B243</t>
+          <t>B256</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5559,13 +5545,13 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -5593,7 +5579,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>B244</t>
+          <t>B257</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5617,13 +5603,13 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -5651,7 +5637,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>B245</t>
+          <t>B258</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5675,13 +5661,13 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>0.61</v>
+        <v>1.03</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0.61</v>
+        <v>1.03</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -5695,11 +5681,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -5708,28 +5694,29 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Капельная воронка с гидрозатвором по типу ТП-21 для отвода конденсата от кондиционеров
-105,11 = [1 279,89 / 1,22 /  10,18] +  2% Заг.скл</t>
+          <t>ОБОРУДОВАНИЕ:
+Вентиляторный модуль 19", 4 вентилятора серый
+1 681,48 = [14 839 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>B249</t>
+          <t>B262</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Вентиляторный модуль 19" 1U Cabeus JG03t 4 вентилятора серый</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.2 [row 22]</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5738,31 +5725,31 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+          <t>[HITL Подтверждено] Объемы соответствуют проектным с учетом допустимого расхода и погрешностей</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>SUSPECT</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -5771,28 +5758,29 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Сифон с воронкой с разрывом струи
-133,38 = [1 624 / 1,22 /  10,18] +  2% Заг.скл</t>
+          <t>ОБОРУДОВАНИЕ:
+Органайзер для кабеля 1U с крышкой 
+94,73 = [836 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>B252</t>
+          <t>B265</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Органайзер для кабеля 1U с крышкой</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.2 [row 27]</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5801,142 +5789,1131 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>5</v>
+        <v>-0.06</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>0.0116</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+          <t>Занижение объема относительно РД</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Прайс-лист</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ОБОРУДОВАНИЕ:
+Выдвижная полка 19" для клавиатуры, серая
+261,99 = [2 312 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>B268</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Выдвижная полка 19" для клавиатуры, серая</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>p.11 [row 91]</t>
+          <t>p.2 [row 25]</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Проектная позиция не осмечена (Пропущенный объем)</t>
+          <t>Объемы соответствуют проектным с учетом допустимого расхода и погрешностей</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>72.3</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Прайс-лист</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ОБОРУДОВАНИЕ:
+Фальш-панель
+36,48 = [322 / 1,22 /  7,54] +  3% Трансп +  1,2% Заг.скл</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>B271</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Фальш-панель 1U Cabeus SH-J019-1U</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>p.2 [row 26]</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>[HITL Подтверждено] Объемы соответствуют проектным с учетом допустимого расхода и погрешностей</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>4.10-27-4
+Поправка: Гл.12.Прил.8.п.8. 3_12.00.01.11.001</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Прокладка и включение перемычки кабельной между секциями одного статива без укладки в кабельном канале</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>B274</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>НР от ФОТ</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>B276</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>90</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>90</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>СП от ФОТ</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>B277</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>46</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>46</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ЗТР</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>B278</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Прайс-лист</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Блок евророзеток для 19" шкафов 16А ,8 розеток
+233,16 = [2 839 / 1,22 /  10,18] +  2% Заг.скл</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>B282</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Блок евророзеток для 19" шкафов 16А Cabeus 8 розеток</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>p.2 [row 23]</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Объемы соответствуют проектным с учетом допустимого расхода и погрешностей</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Прайс-лист</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Набор кабелей заземления 
+95,02 = [1 157 / 1,22 /  10,18] +  2% Заг.скл</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>B285</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Позиция сметы отсутствует в спецификации проекта (Необоснованный объем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>2 САНИТАРНО-ТЕХНИЧЕСКОЕ ОБОРУДОВАНИЕ</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>p.12 [row 113]</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>4</v>
-      </c>
-      <c r="L91" t="n">
-        <v>-4</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="inlineStr">
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2 Оборудование:</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>p.1 [row 1]</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>7</v>
+      </c>
+      <c r="L98" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Проектная позиция не осмечена (Пропущенный объем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Цилиндрическая IP-видеокамера с фиксированным объективом IP 4 Мп;
+размер матрицы 1/2.9"; встроенный микрофон; Дальность ИК подсветки
+80м; режим "день/ночь"; PoE 7 Вт; -40 ~ +60°C,</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>p.1 [row 2]</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>5</v>
+      </c>
+      <c r="L99" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Проектная позиция не осмечена (Пропущенный объем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Автоматизированное рабочее место, моноблок</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>p.1 [row 8]</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Проектная позиция не осмечена (Пропущенный объем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Комплект проводных клавиатуры и мыши</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>p.1 [row 9]</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Проектная позиция не осмечена (Пропущенный объем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ИБП 1500 Вт, On-Line, синус, встр. АКБ 36В (3x9Ач), 8хC13 Материалы и кабельные изделия</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>p.1 [row 10]</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Проектная позиция не осмечена (Пропущенный объем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Гофротруба d-20мм</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>p.1 [row 14]</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L103" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Проектная позиция не осмечена (Пропущенный объем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Короб электротехнический 10х12 ПВХ 2м</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>p.1 [row 15]</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>300</v>
+      </c>
+      <c r="L104" t="n">
+        <v>-300</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Проектная позиция не осмечена (Пропущенный объем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Металлорукав герметичный в ПВХ изоляции</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>p.1 [row 16]</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>10</v>
+      </c>
+      <c r="L105" t="n">
+        <v>-10</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Проектная позиция не осмечена (Пропущенный объем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>p.2 [row 19]</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>7</v>
+      </c>
+      <c r="L106" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Проектная позиция не осмечена (Пропущенный объем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Набор кабелей заземления Cabeus GrW</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>p.2 [row 24]</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="inlineStr">
         <is>
           <t>Проектная позиция не осмечена (Пропущенный объем)</t>
         </is>
